--- a/resources/templates/standard/F2100-12.xlsx
+++ b/resources/templates/standard/F2100-12.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>공정별 전담자 및 대체자 관리기준</t>
   </si>
@@ -636,12 +639,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -679,15 +684,15 @@
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
       <c r="AO1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -792,7 +797,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -843,17 +848,17 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -864,19 +869,19 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
       <c r="T5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="8"/>
       <c r="Z5" s="8"/>
@@ -888,7 +893,7 @@
       <c r="AF5" s="8"/>
       <c r="AG5" s="8"/>
       <c r="AH5" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
@@ -899,7 +904,7 @@
       <c r="AO5" s="8"/>
       <c r="AP5" s="8"/>
       <c r="AQ5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR5" s="8"/>
       <c r="AS5" s="8"/>
@@ -1937,7 +1942,7 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
